--- a/etf_holdings/2026-10-14_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-10-14_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1486,97 +1486,133 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2368</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
+          <t>2059</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>川湖</t>
+        </is>
+      </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>金像電</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
+          <t>川湖</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2.29%</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.52%</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>1.81%</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-0.48%</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>50000</v>
+      </c>
       <c r="K18" t="n">
-        <v>156000</v>
-      </c>
-      <c r="L18" t="inlineStr"/>
+        <v>40000</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-10,000</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-10-13_00990A_full_holdings.xlsx</t>
+          <t>2026-10-13_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3443</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
+          <t>2615</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>萬海</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>創意</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
+          <t>萬海</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0.71%</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.51%</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>1.01%</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>+0.30%</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>1350000</v>
+      </c>
       <c r="K19" t="n">
-        <v>23000</v>
-      </c>
-      <c r="L19" t="inlineStr"/>
+        <v>1850000</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>500,000</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-10-13_00990A_full_holdings.xlsx</t>
+          <t>2026-10-13_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00400A</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1591,37 +1627,37 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0091</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>50SAMSUNG ELECTRO-MECHANICS CO</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.71%</t>
+          <t>0.05%</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
-        <v>7234</v>
+        <v>241040</v>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-10-13_00990A_full_holdings.xlsx</t>
+          <t>2026-10-13_00400A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00400A</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1636,55 +1672,55 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2.29%</t>
+          <t>4.10%</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>2.77%</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.48%</t>
+          <t>-1.33%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>50000</v>
+        <v>669000</v>
       </c>
       <c r="K21" t="n">
-        <v>40000</v>
+        <v>475000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-10,000</t>
+          <t>-194,000</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-10-13_00407A_full_holdings.xlsx</t>
+          <t>2026-10-13_00400A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00400A</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1699,48 +1735,48 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.71%</t>
+          <t>8.47%</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>8.96%</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>+0.30%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>1350000</v>
+        <v>1034000</v>
       </c>
       <c r="K22" t="n">
-        <v>1850000</v>
+        <v>1094000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>500,000</t>
+          <t>60,000</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-10-13_00407A_full_holdings.xlsx</t>
+          <t>2026-10-13_00400A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
@@ -1752,37 +1788,55 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>元大金</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.05%</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
+          <t>1.51%</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>1.95%</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>+0.44%</t>
+        </is>
+      </c>
       <c r="J23" t="n">
-        <v>241040</v>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
+        <v>378000</v>
+      </c>
+      <c r="K23" t="n">
+        <v>507000</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>129,000</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
           <t>2026-10-13_00400A_full_holdings.xlsx</t>
@@ -1807,43 +1861,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>4.10%</t>
+          <t>5.59%</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2.77%</t>
+          <t>4.63%</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-1.33%</t>
+          <t>-0.96%</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>669000</v>
+        <v>282000</v>
       </c>
       <c r="K24" t="n">
-        <v>475000</v>
+        <v>254000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-194,000</t>
+          <t>-28,000</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1870,43 +1924,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>8.47%</t>
+          <t>0.96%</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>8.96%</t>
+          <t>1.62%</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>+0.66%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>1034000</v>
+        <v>1169000</v>
       </c>
       <c r="K25" t="n">
-        <v>1094000</v>
+        <v>1871000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>60,000</t>
+          <t>702,000</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1933,43 +1987,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2637</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>慧洋-KY</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>慧洋-KY</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>0.27%</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1.95%</t>
+          <t>0.48%</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>+0.44%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>378000</v>
+        <v>834000</v>
       </c>
       <c r="K26" t="n">
-        <v>507000</v>
+        <v>1424000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>129,000</t>
+          <t>590,000</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -1991,48 +2045,48 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>5.59%</t>
+          <t>0.69%</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>4.63%</t>
+          <t>1.54%</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-0.96%</t>
+          <t>+0.85%</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>282000</v>
+        <v>3054000</v>
       </c>
       <c r="K27" t="n">
-        <v>254000</v>
+        <v>6547000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-28,000</t>
+          <t>3,493,000</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2059,43 +2113,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>1.20%</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>1.70%</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>+0.66%</t>
+          <t>+0.50%</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>1169000</v>
+        <v>51000</v>
       </c>
       <c r="K28" t="n">
-        <v>1871000</v>
+        <v>71000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>702,000</t>
+          <t>20,000</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2117,48 +2171,48 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2637</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>慧洋-KY</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>慧洋-KY</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>4.12%</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>3.55%</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>+0.21%</t>
+          <t>-0.57%</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>834000</v>
+        <v>377000</v>
       </c>
       <c r="K29" t="n">
-        <v>1424000</v>
+        <v>329000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>590,000</t>
+          <t>-48,000</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2180,48 +2234,48 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.69%</t>
+          <t>4.89%</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1.54%</t>
+          <t>4.15%</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>+0.85%</t>
+          <t>-0.74%</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>3054000</v>
+        <v>1209000</v>
       </c>
       <c r="K30" t="n">
-        <v>6547000</v>
+        <v>1069000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>3,493,000</t>
+          <t>-140,000</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2248,43 +2302,43 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>0.50%</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1.70%</t>
+          <t>0.99%</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>+0.50%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>51000</v>
+        <v>819000</v>
       </c>
       <c r="K31" t="n">
-        <v>71000</v>
+        <v>1614000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>795,000</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2311,43 +2365,43 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>4.12%</t>
+          <t>4.06%</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>3.55%</t>
+          <t>3.54%</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>-0.57%</t>
+          <t>-0.52%</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>377000</v>
+        <v>176000</v>
       </c>
       <c r="K32" t="n">
-        <v>329000</v>
+        <v>154000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-48,000</t>
+          <t>-22,000</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2374,235 +2428,46 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>4.89%</t>
+          <t>3.22%</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>4.15%</t>
+          <t>2.08%</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>-0.74%</t>
+          <t>-1.14%</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>1209000</v>
+        <v>596000</v>
       </c>
       <c r="K33" t="n">
-        <v>1069000</v>
+        <v>396000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-140,000</t>
+          <t>-200,000</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
-        <is>
-          <t>2026-10-13_00400A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>3231</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>緯創</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>緯創</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>0.50%</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>0.99%</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>+0.49%</t>
-        </is>
-      </c>
-      <c r="J34" t="n">
-        <v>819000</v>
-      </c>
-      <c r="K34" t="n">
-        <v>1614000</v>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>795,000</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>2026-10-13_00400A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>3653</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>健策</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>健策</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>4.06%</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>3.54%</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>-0.52%</t>
-        </is>
-      </c>
-      <c r="J35" t="n">
-        <v>176000</v>
-      </c>
-      <c r="K35" t="n">
-        <v>154000</v>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>-22,000</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>2026-10-13_00400A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>6187</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>萬潤</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>萬潤</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>3.22%</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>2.08%</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>-1.14%</t>
-        </is>
-      </c>
-      <c r="J36" t="n">
-        <v>596000</v>
-      </c>
-      <c r="K36" t="n">
-        <v>396000</v>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>-200,000</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
         <is>
           <t>2026-10-13_00400A_full_holdings.xlsx</t>
         </is>

--- a/etf_holdings/2026-10-14_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-10-14_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00981A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,55 +501,55 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>10.30%</t>
+          <t>0.14%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>10.79%</t>
+          <t>0.21%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>11824000</v>
+        <v>800000</v>
       </c>
       <c r="K2" t="n">
-        <v>12188000</v>
+        <v>1200000</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>364,000</t>
+          <t>400,000</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-10-13_00981A_full_holdings.xlsx</t>
+          <t>2026-10-13_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00981A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -564,55 +564,55 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>9.81%</t>
+          <t>0.16%</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>8.53%</t>
+          <t>0.08%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.28%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>4650000</v>
+        <v>1300000</v>
       </c>
       <c r="K3" t="n">
-        <v>4328000</v>
+        <v>700000</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-322,000</t>
+          <t>-600,000</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-10-13_00981A_full_holdings.xlsx</t>
+          <t>2026-10-13_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00981A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -627,55 +627,55 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>7.04%</t>
+          <t>1.24%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>7.17%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>6062000</v>
+        <v>243000</v>
       </c>
       <c r="K4" t="n">
-        <v>6147000</v>
+        <v>335000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>85,000</t>
+          <t>92,000</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-10-13_00981A_full_holdings.xlsx</t>
+          <t>2026-10-13_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00981A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -685,60 +685,60 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>4.03%</t>
+          <t>6.83%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4.03%</t>
+          <t>5.95%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-0.88%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>6771000</v>
+        <v>7800000</v>
       </c>
       <c r="K5" t="n">
-        <v>6847000</v>
+        <v>7000000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>76,000</t>
+          <t>-800,000</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-10-13_00981A_full_holdings.xlsx</t>
+          <t>2026-10-13_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>00981A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -748,60 +748,60 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>0.54%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.22%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>476000</v>
+        <v>700000</v>
       </c>
       <c r="K6" t="n">
-        <v>576000</v>
+        <v>300000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>100,000</t>
+          <t>-400,000</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-10-13_00981A_full_holdings.xlsx</t>
+          <t>2026-10-13_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -816,236 +816,190 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.38%</t>
+          <t>2.16%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.72%</t>
+          <t>2.32%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>8500000</v>
+        <v>1800000</v>
       </c>
       <c r="K7" t="n">
-        <v>8700000</v>
+        <v>1880000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>200,000</t>
+          <t>80,000</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-10-13_00991A_full_holdings.xlsx</t>
+          <t>2026-10-13_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00990A</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>新增</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>新納入</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2308</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>台達電</t>
-        </is>
-      </c>
+          <t>2368</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>台達電</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>1.64%</t>
-        </is>
-      </c>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>&lt;0.01%</t>
+          <t>0.52%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="n">
-        <v>650000</v>
-      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>-649,000</t>
-        </is>
-      </c>
+        <v>156000</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-10-13_00991A_full_holdings.xlsx</t>
+          <t>2026-10-13_00990A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00990A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>新增</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>新納入</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3008</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>大立光</t>
-        </is>
-      </c>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>大立光</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>&lt;0.01%</t>
-        </is>
-      </c>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>0.51%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="n">
-        <v>1000</v>
-      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
-        <v>110000</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>109,000</t>
-        </is>
-      </c>
+        <v>23000</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-10-13_00991A_full_holdings.xlsx</t>
+          <t>2026-10-13_00990A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00990A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>0091</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>欣興</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>欣興</t>
-        </is>
-      </c>
+          <t>50SAMSUNG ELECTRO-MECHANICS CO</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>8.60%</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>8.47%</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>-0.13%</t>
-        </is>
-      </c>
+          <t>0.71%</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
-        <v>5280000</v>
-      </c>
-      <c r="K10" t="n">
-        <v>5350000</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>70,000</t>
-        </is>
-      </c>
+        <v>7234</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-10-13_00991A_full_holdings.xlsx</t>
+          <t>2026-10-13_00990A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1055,60 +1009,60 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>6505</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>2.29%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.60%</t>
+          <t>1.81%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>+0.40%</t>
+          <t>-0.48%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>8500000</v>
+        <v>50000</v>
       </c>
       <c r="K11" t="n">
-        <v>10000000</v>
+        <v>40000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1,500,000</t>
+          <t>-10,000</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-10-13_00991A_full_holdings.xlsx</t>
+          <t>2026-10-13_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1123,118 +1077,100 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.14%</t>
+          <t>0.71%</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>1.01%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.30%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>800000</v>
+        <v>1350000</v>
       </c>
       <c r="K12" t="n">
-        <v>1200000</v>
+        <v>1850000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>400,000</t>
+          <t>500,000</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-10-13_00403A_full_holdings.xlsx</t>
+          <t>2026-10-13_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00400A</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>強茂</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>強茂</t>
-        </is>
-      </c>
+          <t>元大金</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.16%</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.08%</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>-0.08%</t>
-        </is>
-      </c>
+          <t>0.05%</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>1300000</v>
-      </c>
-      <c r="K13" t="n">
-        <v>700000</v>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>-600,000</t>
-        </is>
-      </c>
+        <v>241040</v>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-10-13_00403A_full_holdings.xlsx</t>
+          <t>2026-10-13_00400A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00400A</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1244,60 +1180,60 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>4.10%</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1.75%</t>
+          <t>2.77%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-1.33%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>243000</v>
+        <v>669000</v>
       </c>
       <c r="K14" t="n">
-        <v>335000</v>
+        <v>475000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>92,000</t>
+          <t>-194,000</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-10-13_00403A_full_holdings.xlsx</t>
+          <t>2026-10-13_00400A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00400A</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1307,60 +1243,60 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>6.83%</t>
+          <t>8.47%</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>5.95%</t>
+          <t>8.96%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.88%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>7800000</v>
+        <v>1034000</v>
       </c>
       <c r="K15" t="n">
-        <v>7000000</v>
+        <v>1094000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-800,000</t>
+          <t>60,000</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-10-13_00403A_full_holdings.xlsx</t>
+          <t>2026-10-13_00400A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00400A</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1370,60 +1306,60 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>1.51%</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>1.95%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>+0.44%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>700000</v>
+        <v>378000</v>
       </c>
       <c r="K16" t="n">
-        <v>300000</v>
+        <v>507000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-400,000</t>
+          <t>129,000</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-10-13_00403A_full_holdings.xlsx</t>
+          <t>2026-10-13_00400A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00400A</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1433,60 +1369,60 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2.16%</t>
+          <t>5.59%</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2.32%</t>
+          <t>4.63%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-0.96%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>1800000</v>
+        <v>282000</v>
       </c>
       <c r="K17" t="n">
-        <v>1880000</v>
+        <v>254000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>80,000</t>
+          <t>-28,000</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-10-13_00403A_full_holdings.xlsx</t>
+          <t>2026-10-13_00400A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00400A</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1496,60 +1432,60 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2.29%</t>
+          <t>0.96%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>1.62%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.48%</t>
+          <t>+0.66%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>50000</v>
+        <v>1169000</v>
       </c>
       <c r="K18" t="n">
-        <v>40000</v>
+        <v>1871000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-10,000</t>
+          <t>702,000</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-10-13_00407A_full_holdings.xlsx</t>
+          <t>2026-10-13_00400A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00400A</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1564,48 +1500,48 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>2637</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>慧洋-KY</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>慧洋-KY</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.71%</t>
+          <t>0.27%</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>0.48%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>+0.30%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>1350000</v>
+        <v>834000</v>
       </c>
       <c r="K19" t="n">
-        <v>1850000</v>
+        <v>1424000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>500,000</t>
+          <t>590,000</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-10-13_00407A_full_holdings.xlsx</t>
+          <t>2026-10-13_00400A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
@@ -1617,37 +1553,55 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>元大金</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
+          <t>中信金</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>中信金</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.05%</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
+          <t>0.69%</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>1.54%</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>+0.85%</t>
+        </is>
+      </c>
       <c r="J20" t="n">
-        <v>241040</v>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
+        <v>3054000</v>
+      </c>
+      <c r="K20" t="n">
+        <v>6547000</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>3,493,000</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
           <t>2026-10-13_00400A_full_holdings.xlsx</t>
@@ -1667,48 +1621,48 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>4.10%</t>
+          <t>1.20%</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2.77%</t>
+          <t>1.70%</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.33%</t>
+          <t>+0.50%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>669000</v>
+        <v>51000</v>
       </c>
       <c r="K21" t="n">
-        <v>475000</v>
+        <v>71000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-194,000</t>
+          <t>20,000</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1730,48 +1684,48 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>8.47%</t>
+          <t>4.12%</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>8.96%</t>
+          <t>3.55%</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>-0.57%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>1034000</v>
+        <v>377000</v>
       </c>
       <c r="K22" t="n">
-        <v>1094000</v>
+        <v>329000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>60,000</t>
+          <t>-48,000</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1793,48 +1747,48 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>4.89%</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1.95%</t>
+          <t>4.15%</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>+0.44%</t>
+          <t>-0.74%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>378000</v>
+        <v>1209000</v>
       </c>
       <c r="K23" t="n">
-        <v>507000</v>
+        <v>1069000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>129,000</t>
+          <t>-140,000</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1856,48 +1810,48 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>5.59%</t>
+          <t>0.50%</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>4.63%</t>
+          <t>0.99%</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-0.96%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>282000</v>
+        <v>819000</v>
       </c>
       <c r="K24" t="n">
-        <v>254000</v>
+        <v>1614000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-28,000</t>
+          <t>795,000</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1919,48 +1873,48 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>4.06%</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>3.54%</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>+0.66%</t>
+          <t>-0.52%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>1169000</v>
+        <v>176000</v>
       </c>
       <c r="K25" t="n">
-        <v>1871000</v>
+        <v>154000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>702,000</t>
+          <t>-22,000</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1982,492 +1936,51 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2637</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>慧洋-KY</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>慧洋-KY</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>3.22%</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>2.08%</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>+0.21%</t>
+          <t>-1.14%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>834000</v>
+        <v>596000</v>
       </c>
       <c r="K26" t="n">
-        <v>1424000</v>
+        <v>396000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>590,000</t>
+          <t>-200,000</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
-        <is>
-          <t>2026-10-13_00400A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2891</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>中信金</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>中信金</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>0.69%</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>1.54%</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>+0.85%</t>
-        </is>
-      </c>
-      <c r="J27" t="n">
-        <v>3054000</v>
-      </c>
-      <c r="K27" t="n">
-        <v>6547000</v>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>3,493,000</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>2026-10-13_00400A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>3008</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>大立光</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>大立光</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>1.20%</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>1.70%</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>+0.50%</t>
-        </is>
-      </c>
-      <c r="J28" t="n">
-        <v>51000</v>
-      </c>
-      <c r="K28" t="n">
-        <v>71000</v>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>20,000</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>2026-10-13_00400A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>3017</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>奇鋐</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>奇鋐</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>4.12%</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>3.55%</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>-0.57%</t>
-        </is>
-      </c>
-      <c r="J29" t="n">
-        <v>377000</v>
-      </c>
-      <c r="K29" t="n">
-        <v>329000</v>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>-48,000</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>2026-10-13_00400A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>3037</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>欣興</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>欣興</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>4.89%</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>4.15%</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>-0.74%</t>
-        </is>
-      </c>
-      <c r="J30" t="n">
-        <v>1209000</v>
-      </c>
-      <c r="K30" t="n">
-        <v>1069000</v>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>-140,000</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>2026-10-13_00400A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>3231</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>緯創</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>緯創</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>0.50%</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>0.99%</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>+0.49%</t>
-        </is>
-      </c>
-      <c r="J31" t="n">
-        <v>819000</v>
-      </c>
-      <c r="K31" t="n">
-        <v>1614000</v>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>795,000</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>2026-10-13_00400A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>3653</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>健策</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>健策</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>4.06%</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>3.54%</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>-0.52%</t>
-        </is>
-      </c>
-      <c r="J32" t="n">
-        <v>176000</v>
-      </c>
-      <c r="K32" t="n">
-        <v>154000</v>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>-22,000</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>2026-10-13_00400A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>6187</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>萬潤</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>萬潤</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>3.22%</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>2.08%</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>-1.14%</t>
-        </is>
-      </c>
-      <c r="J33" t="n">
-        <v>596000</v>
-      </c>
-      <c r="K33" t="n">
-        <v>396000</v>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>-200,000</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
         <is>
           <t>2026-10-13_00400A_full_holdings.xlsx</t>
         </is>

--- a/etf_holdings/2026-10-14_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-10-14_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,55 +501,55 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.14%</t>
+          <t>10.30%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>10.73%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>800000</v>
+        <v>11824000</v>
       </c>
       <c r="K2" t="n">
-        <v>1200000</v>
+        <v>12188000</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>400,000</t>
+          <t>364,000</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-10-13_00403A_full_holdings.xlsx</t>
+          <t>2026-10-13_00981A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -559,60 +559,60 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.16%</t>
+          <t>1.58%</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.08%</t>
+          <t>2.42%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.84%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>1300000</v>
+        <v>3741000</v>
       </c>
       <c r="K3" t="n">
-        <v>700000</v>
+        <v>5423000</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-600,000</t>
+          <t>1,682,000</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-10-13_00403A_full_holdings.xlsx</t>
+          <t>2026-10-13_00981A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -622,60 +622,60 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>9.81%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.75%</t>
+          <t>8.45%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-1.36%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>243000</v>
+        <v>4650000</v>
       </c>
       <c r="K4" t="n">
-        <v>335000</v>
+        <v>4328000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>92,000</t>
+          <t>-322,000</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-10-13_00403A_full_holdings.xlsx</t>
+          <t>2026-10-13_00981A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -685,60 +685,60 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>6.83%</t>
+          <t>7.04%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5.95%</t>
+          <t>7.21%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.88%</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>7800000</v>
+        <v>6062000</v>
       </c>
       <c r="K5" t="n">
-        <v>7000000</v>
+        <v>6147000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-800,000</t>
+          <t>85,000</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-10-13_00403A_full_holdings.xlsx</t>
+          <t>2026-10-13_00981A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -748,60 +748,60 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>0.12%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>700000</v>
+        <v>1000</v>
       </c>
       <c r="K6" t="n">
-        <v>300000</v>
+        <v>1257000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-400,000</t>
+          <t>1,256,000</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-10-13_00403A_full_holdings.xlsx</t>
+          <t>2026-10-13_00981A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -816,190 +816,244 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2.16%</t>
+          <t>1.90%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.32%</t>
+          <t>2.19%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>+0.29%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1800000</v>
+        <v>684000</v>
       </c>
       <c r="K7" t="n">
-        <v>1880000</v>
+        <v>751000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>80,000</t>
+          <t>67,000</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-10-13_00403A_full_holdings.xlsx</t>
+          <t>2026-10-13_00981A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2368</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
+          <t>4979</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>華星光</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>金像電</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>華星光</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.52%</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>0.20%</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>+0.20%</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>1000</v>
+      </c>
       <c r="K8" t="n">
-        <v>156000</v>
-      </c>
-      <c r="L8" t="inlineStr"/>
+        <v>957000</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>956,000</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-10-13_00990A_full_holdings.xlsx</t>
+          <t>2026-10-13_00981A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3443</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
+          <t>5274</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>信驊</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>創意</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+          <t>信驊</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0.96%</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.51%</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>1.16%</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>+0.20%</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>157900</v>
+      </c>
       <c r="K9" t="n">
-        <v>23000</v>
-      </c>
-      <c r="L9" t="inlineStr"/>
+        <v>186900</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>29,000</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-10-13_00990A_full_holdings.xlsx</t>
+          <t>2026-10-13_00981A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0091</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>50SAMSUNG ELECTRO-MECHANICS CO</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.71%</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+          <t>4.03%</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>4.20%</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>+0.17%</t>
+        </is>
+      </c>
       <c r="J10" t="n">
-        <v>7234</v>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+        <v>6771000</v>
+      </c>
+      <c r="K10" t="n">
+        <v>6847000</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>76,000</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-10-13_00990A_full_holdings.xlsx</t>
+          <t>2026-10-13_00981A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1009,60 +1063,60 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2.29%</t>
+          <t>0.49%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>0.54%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.48%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>50000</v>
+        <v>420000</v>
       </c>
       <c r="K11" t="n">
-        <v>40000</v>
+        <v>470000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-10,000</t>
+          <t>50,000</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-10-13_00407A_full_holdings.xlsx</t>
+          <t>2026-10-13_00981A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1072,105 +1126,123 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.71%</t>
+          <t>3.37%</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>2.45%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>+0.30%</t>
+          <t>-0.92%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1350000</v>
+        <v>4315561</v>
       </c>
       <c r="K12" t="n">
-        <v>1850000</v>
+        <v>3281561</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>500,000</t>
+          <t>-1,034,000</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-10-13_00407A_full_holdings.xlsx</t>
+          <t>2026-10-13_00981A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>元大金</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.05%</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
+          <t>0.28%</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.41%</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>+0.13%</t>
+        </is>
+      </c>
       <c r="J13" t="n">
-        <v>241040</v>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+        <v>476000</v>
+      </c>
+      <c r="K13" t="n">
+        <v>696000</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>220,000</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-10-13_00400A_full_holdings.xlsx</t>
+          <t>2026-10-13_00981A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00991A</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1180,60 +1252,60 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4.10%</t>
+          <t>3.38%</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2.77%</t>
+          <t>+0.35%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.33%</t>
+          <t>-3.03%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>669000</v>
+        <v>8500000</v>
       </c>
       <c r="K14" t="n">
-        <v>475000</v>
+        <v>8700000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-194,000</t>
+          <t>200,000</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-10-13_00400A_full_holdings.xlsx</t>
+          <t>2026-10-13_00991A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00991A</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1243,60 +1315,60 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>8.47%</t>
+          <t>1.64%</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>8.96%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>-1.64%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>1034000</v>
+        <v>650000</v>
       </c>
       <c r="K15" t="n">
-        <v>1094000</v>
+        <v>1000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>60,000</t>
+          <t>-649,000</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-10-13_00400A_full_holdings.xlsx</t>
+          <t>2026-10-13_00991A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00991A</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1311,39 +1383,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>&lt;0.01%</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.95%</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>+0.44%</t>
-        </is>
-      </c>
+          <t>-0.07%</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="n">
-        <v>378000</v>
+        <v>1000</v>
       </c>
       <c r="K16" t="n">
-        <v>507000</v>
+        <v>130000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1352,14 +1420,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-10-13_00400A_full_holdings.xlsx</t>
+          <t>2026-10-13_00991A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00991A</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1369,60 +1437,60 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>5.59%</t>
+          <t>8.60%</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4.63%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.96%</t>
+          <t>-8.56%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>282000</v>
+        <v>5280000</v>
       </c>
       <c r="K17" t="n">
-        <v>254000</v>
+        <v>5350000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-28,000</t>
+          <t>70,000</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-10-13_00400A_full_holdings.xlsx</t>
+          <t>2026-10-13_00991A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00991A</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1437,55 +1505,55 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>6505</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>台塑化</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>台塑化</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>1.20%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>+0.66%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>1169000</v>
+        <v>8500000</v>
       </c>
       <c r="K18" t="n">
-        <v>1871000</v>
+        <v>10000000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>702,000</t>
+          <t>1,500,000</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-10-13_00400A_full_holdings.xlsx</t>
+          <t>2026-10-13_00991A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1495,123 +1563,105 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2637</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>慧洋-KY</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>慧洋-KY</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.53%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>+0.21%</t>
+          <t>-0.47%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>834000</v>
+        <v>3344000</v>
       </c>
       <c r="K19" t="n">
-        <v>1424000</v>
+        <v>1672000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>590,000</t>
+          <t>-1,672,000</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-10-13_00400A_full_holdings.xlsx</t>
+          <t>2026-10-13_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>中信金</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>中信金</t>
-        </is>
-      </c>
+          <t>鴻勁</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.69%</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>1.54%</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>+0.85%</t>
-        </is>
-      </c>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
-        <v>3054000</v>
-      </c>
-      <c r="K20" t="n">
-        <v>6547000</v>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>3,493,000</t>
-        </is>
-      </c>
+        <v>1000</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-10-13_00400A_full_holdings.xlsx</t>
+          <t>2026-10-13_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1621,60 +1671,60 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>2.03%</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.70%</t>
+          <t>1.53%</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>+0.50%</t>
+          <t>-0.50%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>51000</v>
+        <v>20000000</v>
       </c>
       <c r="K21" t="n">
-        <v>71000</v>
+        <v>15000000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>-5,000,000</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-10-13_00400A_full_holdings.xlsx</t>
+          <t>2026-10-13_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1684,60 +1734,60 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>4.12%</t>
+          <t>0.14%</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>3.55%</t>
+          <t>0.22%</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.57%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>377000</v>
+        <v>800000</v>
       </c>
       <c r="K22" t="n">
-        <v>329000</v>
+        <v>1200000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-48,000</t>
+          <t>400,000</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-10-13_00400A_full_holdings.xlsx</t>
+          <t>2026-10-13_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1752,55 +1802,55 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>4.89%</t>
+          <t>0.16%</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>4.15%</t>
+          <t>0.04%</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.74%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>1209000</v>
+        <v>1300000</v>
       </c>
       <c r="K23" t="n">
-        <v>1069000</v>
+        <v>350000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-140,000</t>
+          <t>-950,000</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-10-13_00400A_full_holdings.xlsx</t>
+          <t>2026-10-13_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1815,55 +1865,55 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>1.24%</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>1.65%</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>+0.41%</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>819000</v>
+        <v>243000</v>
       </c>
       <c r="K24" t="n">
-        <v>1614000</v>
+        <v>335000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>795,000</t>
+          <t>92,000</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-10-13_00400A_full_holdings.xlsx</t>
+          <t>2026-10-13_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1878,109 +1928,3799 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>4.06%</t>
+          <t>6.83%</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>3.54%</t>
+          <t>5.95%</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-0.52%</t>
+          <t>-0.88%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>176000</v>
+        <v>7800000</v>
       </c>
       <c r="K25" t="n">
-        <v>154000</v>
+        <v>7000000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-22,000</t>
+          <t>-800,000</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-10-13_00400A_full_holdings.xlsx</t>
+          <t>2026-10-13_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>3.62%</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>3.87%</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>+0.25%</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>640000</v>
+      </c>
+      <c r="K26" t="n">
+        <v>655000</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>15,000</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>2026-10-13_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>5274</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>信驊</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>信驊</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1.45%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>1.83%</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>+0.38%</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>117500</v>
+      </c>
+      <c r="K27" t="n">
+        <v>145500</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>28,000</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2026-10-13_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>6274</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2.54%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2.71%</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>+0.17%</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>2100000</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2180000</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>80,000</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2026-10-13_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>6488</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>環球晶</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>環球晶</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>0.54%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>0.22%</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>-0.32%</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>700000</v>
+      </c>
+      <c r="K29" t="n">
+        <v>300000</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>-400,000</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>2026-10-13_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>8996</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2.16%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2.27%</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>+0.11%</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1880000</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>80,000</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>2026-10-13_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>00990A</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2368</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>0.50%</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="n">
+        <v>156000</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>2026-10-13_00990A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>00990A</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>0.51%</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="n">
+        <v>23000</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>2026-10-13_00990A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>00990A</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>0091</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>50SAMSUNG ELECTRO-MECHANICS CO</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>0.71%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="n">
+        <v>7234</v>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>2026-10-13_00990A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>00990A</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2308</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>台達電</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>台達電</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>3.33%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>2.04%</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>-1.29%</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>633000</v>
+      </c>
+      <c r="K34" t="n">
+        <v>420000</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>-213,000</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>2026-10-13_00990A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>00990A</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>6981</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>MURATA MANUFACTURING CO LTD</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>MURATA MANUFACTURING CO LTD</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>1.87%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>0.74%</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>-1.13%</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>418400</v>
+      </c>
+      <c r="K35" t="n">
+        <v>174300</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>-244,100</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>2026-10-13_00990A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>00407A</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>3533</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>嘉澤</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>0.47%</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="n">
+        <v>54000</v>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>2026-10-13_00407A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>00407A</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2412</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>中華電</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>0.04%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="n">
+        <v>64000</v>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2026-10-13_00407A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>00407A</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2059</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>川湖</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>川湖</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2.29%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>1.79%</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>-0.50%</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>50000</v>
+      </c>
+      <c r="K38" t="n">
+        <v>40000</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>-10,000</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2026-10-13_00407A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>00407A</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2368</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>0.60%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>1.33%</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>+0.73%</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>113000</v>
+      </c>
+      <c r="K39" t="n">
+        <v>236000</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>123,000</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2026-10-13_00407A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>00407A</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2615</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>萬海</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>萬海</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>0.71%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>1.03%</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>+0.32%</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>1350000</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1850000</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>500,000</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2026-10-13_00407A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>00407A</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>5.02%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>4.72%</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>-0.30%</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>143000</v>
+      </c>
+      <c r="K41" t="n">
+        <v>128000</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>-15,000</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2026-10-13_00407A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>00407A</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>8996</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2.41%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>1.35%</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>-1.06%</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>324000</v>
+      </c>
+      <c r="K42" t="n">
+        <v>179000</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>-145,000</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2026-10-13_00407A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2368</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>0.30%</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="n">
+        <v>26000</v>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2481</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>強茂</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>0.26%</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="n">
+        <v>159000</v>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>5347</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>世界</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>0.31%</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="n">
+        <v>177000</v>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>6271</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>同欣電</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>0.27%</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="n">
+        <v>114000</v>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>8996</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>1.71%</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="n">
+        <v>100000</v>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>1560</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>中砂</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>中砂</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>1.67%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>1.68%</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>174000</v>
+      </c>
+      <c r="K48" t="n">
+        <v>178000</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2059</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>川湖</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>川湖</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>1.12%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>1.00%</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>-0.12%</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>11000</v>
+      </c>
+      <c r="K49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>光寶科</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>光寶科</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.62%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.62%</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>222000</v>
+      </c>
+      <c r="K50" t="n">
+        <v>227000</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2313</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>華通</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>華通</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.45%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.46%</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>185000</v>
+      </c>
+      <c r="K51" t="n">
+        <v>189000</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>8.35%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>8.26%</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>-0.09%</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>341000</v>
+      </c>
+      <c r="K52" t="n">
+        <v>333000</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>-8,000</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>0.52%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>0.55%</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>+0.03%</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>23000</v>
+      </c>
+      <c r="K53" t="n">
+        <v>25000</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2383</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>6.27%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>6.23%</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>-0.04%</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>106000</v>
+      </c>
+      <c r="K54" t="n">
+        <v>113000</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2404</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>漢唐</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>漢唐</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>0.48%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>0.48%</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>40000</v>
+      </c>
+      <c r="K55" t="n">
+        <v>42000</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>1.51%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>1.48%</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>-0.03%</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>34000</v>
+      </c>
+      <c r="K56" t="n">
+        <v>33000</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2467</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>志聖</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>志聖</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>0.55%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>0.54%</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>96000</v>
+      </c>
+      <c r="K57" t="n">
+        <v>98000</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>6.26%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>6.17%</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>-0.09%</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>518000</v>
+      </c>
+      <c r="K58" t="n">
+        <v>526000</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>3042</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>晶技</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>晶技</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>0.58%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>0.60%</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>+0.02%</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>296000</v>
+      </c>
+      <c r="K59" t="n">
+        <v>310000</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>14,000</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>3044</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>健鼎</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>健鼎</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>0.75%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>0.77%</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>+0.02%</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>134000</v>
+      </c>
+      <c r="K60" t="n">
+        <v>136000</v>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>3081</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>聯亞</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>聯亞</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>1.34%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>1.33%</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>46000</v>
+      </c>
+      <c r="K61" t="n">
+        <v>49000</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>3105</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>穩懋</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>穩懋</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>1.14%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>1.18%</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>+0.04%</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>204000</v>
+      </c>
+      <c r="K62" t="n">
+        <v>214000</v>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>3264</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>欣銓</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>欣銓</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>0.56%</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>0.58%</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>+0.02%</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>214000</v>
+      </c>
+      <c r="K63" t="n">
+        <v>219000</v>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>3491</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>昇達科</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>昇達科</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>0.91%</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>0.92%</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>62000</v>
+      </c>
+      <c r="K64" t="n">
+        <v>64000</v>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>3711</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>1.82%</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>1.85%</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>+0.03%</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>248000</v>
+      </c>
+      <c r="K65" t="n">
+        <v>252000</v>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>4958</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2.30%</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>2.34%</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>+0.04%</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>411000</v>
+      </c>
+      <c r="K66" t="n">
+        <v>427000</v>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>16,000</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>6187</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>萬潤</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>萬潤</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>1.95%</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>1.99%</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>+0.04%</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>121000</v>
+      </c>
+      <c r="K67" t="n">
+        <v>125000</v>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>6257</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>矽格</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>矽格</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>1.07%</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>1.10%</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>+0.03%</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>387000</v>
+      </c>
+      <c r="K68" t="n">
+        <v>396000</v>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>6274</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>4.07%</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>4.10%</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>+0.03%</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>244000</v>
+      </c>
+      <c r="K69" t="n">
+        <v>249000</v>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>4.27%</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>2.17%</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>-2.10%</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>195191</v>
+      </c>
+      <c r="K70" t="n">
+        <v>99191</v>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>-96,000</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
           <t>00400A</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>6147</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>頎邦</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>0.97%</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="n">
+        <v>1293000</v>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>2026-10-13_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2885</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>元大金</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>0.05%</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="n">
+        <v>241040</v>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>2026-10-13_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2303</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>0.98%</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>1.93%</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>+0.95%</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>2096000</v>
+      </c>
+      <c r="K73" t="n">
+        <v>4192000</v>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>2,096,000</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>2026-10-13_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2308</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>台達電</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>台達電</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>4.10%</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>2.75%</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>-1.35%</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>669000</v>
+      </c>
+      <c r="K74" t="n">
+        <v>475000</v>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>-194,000</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>2026-10-13_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2327</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>國巨*</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>國巨*</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>0.96%</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>1.44%</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>+0.48%</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>469000</v>
+      </c>
+      <c r="K75" t="n">
+        <v>708000</v>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>239,000</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>2026-10-13_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>8.47%</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>8.85%</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>+0.38%</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>1034000</v>
+      </c>
+      <c r="K76" t="n">
+        <v>1094000</v>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>60,000</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>2026-10-13_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2368</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>1.51%</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>3.00%</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>+1.49%</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>378000</v>
+      </c>
+      <c r="K77" t="n">
+        <v>734000</v>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>356,000</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>2026-10-13_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2383</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>5.59%</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>4.55%</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>-1.04%</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>282000</v>
+      </c>
+      <c r="K78" t="n">
+        <v>254000</v>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>-28,000</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>2026-10-13_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2603</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>長榮</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>長榮</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>0.96%</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>1.60%</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>+0.64%</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>1169000</v>
+      </c>
+      <c r="K79" t="n">
+        <v>1871000</v>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>702,000</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>2026-10-13_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2637</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>慧洋-KY</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>慧洋-KY</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>0.27%</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>0.48%</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>+0.21%</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>834000</v>
+      </c>
+      <c r="K80" t="n">
+        <v>1424000</v>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>590,000</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>2026-10-13_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2891</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>中信金</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>中信金</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>0.69%</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>1.52%</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>+0.83%</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>3054000</v>
+      </c>
+      <c r="K81" t="n">
+        <v>6547000</v>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>3,493,000</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>2026-10-13_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>3008</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>1.20%</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>1.59%</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>+0.39%</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>51000</v>
+      </c>
+      <c r="K82" t="n">
+        <v>71000</v>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>2026-10-13_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>4.12%</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>3.54%</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>-0.58%</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>377000</v>
+      </c>
+      <c r="K83" t="n">
+        <v>329000</v>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>-48,000</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>2026-10-13_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>4.89%</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>4.11%</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>-0.78%</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>1209000</v>
+      </c>
+      <c r="K84" t="n">
+        <v>1069000</v>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>-140,000</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>2026-10-13_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>3044</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>健鼎</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>健鼎</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>1.93%</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>2.52%</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>+0.59%</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>1034000</v>
+      </c>
+      <c r="K85" t="n">
+        <v>1287000</v>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>253,000</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>2026-10-13_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>3231</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>0.50%</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>0.98%</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>+0.48%</t>
+        </is>
+      </c>
+      <c r="J86" t="n">
+        <v>819000</v>
+      </c>
+      <c r="K86" t="n">
+        <v>1614000</v>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>795,000</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>2026-10-13_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>3653</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>4.06%</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>3.54%</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>-0.52%</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>176000</v>
+      </c>
+      <c r="K87" t="n">
+        <v>154000</v>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>-22,000</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>2026-10-13_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
         <is>
           <t>6187</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E88" t="inlineStr">
         <is>
           <t>萬潤</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F88" t="inlineStr">
         <is>
           <t>萬潤</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t>3.22%</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>2.08%</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>-1.14%</t>
-        </is>
-      </c>
-      <c r="J26" t="n">
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>1.48%</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>-1.74%</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
         <v>596000</v>
       </c>
-      <c r="K26" t="n">
-        <v>396000</v>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>-200,000</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
+      <c r="K88" t="n">
+        <v>295000</v>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>-301,000</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
         <is>
           <t>2026-10-13_00400A_full_holdings.xlsx</t>
         </is>

--- a/etf_holdings/2026-10-14_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-10-14_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M88"/>
+  <dimension ref="A1:M151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2291,142 +2291,196 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2368</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
+          <t>1216</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>統一</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>金像電</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
+          <t>統一</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>3.03%</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0.50%</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t>3.37%</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>+0.34%</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>8045000</v>
+      </c>
       <c r="K31" t="n">
-        <v>156000</v>
-      </c>
-      <c r="L31" t="inlineStr"/>
+        <v>10393000</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>2,348,000</t>
+        </is>
+      </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-10-13_00990A_full_holdings.xlsx</t>
+          <t>2026-10-13_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>3443</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr"/>
+          <t>1301</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>台塑</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>創意</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr"/>
+          <t>台塑</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1.21%</t>
+        </is>
+      </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.51%</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+          <t>1.39%</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>+0.18%</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>3022000</v>
+      </c>
       <c r="K32" t="n">
-        <v>23000</v>
-      </c>
-      <c r="L32" t="inlineStr"/>
+        <v>4101000</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>1,079,000</t>
+        </is>
+      </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-10-13_00990A_full_holdings.xlsx</t>
+          <t>2026-10-13_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0091</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>50SAMSUNG ELECTRO-MECHANICS CO</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr"/>
+          <t>大成鋼</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>大成鋼</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.71%</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
+          <t>1.23%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>1.42%</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>+0.19%</t>
+        </is>
+      </c>
       <c r="J33" t="n">
-        <v>7234</v>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
+        <v>5135000</v>
+      </c>
+      <c r="K33" t="n">
+        <v>6940000</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>1,805,000</t>
+        </is>
+      </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-10-13_00990A_full_holdings.xlsx</t>
+          <t>2026-10-13_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2436,60 +2490,60 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>3.33%</t>
+          <t>2.84%</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>2.87%</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>-1.29%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>633000</v>
+        <v>54000</v>
       </c>
       <c r="K34" t="n">
-        <v>420000</v>
+        <v>68000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-213,000</t>
+          <t>14,000</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-10-13_00990A_full_holdings.xlsx</t>
+          <t>2026-10-13_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2504,145 +2558,181 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>6981</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>MURATA MANUFACTURING CO LTD</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>MURATA MANUFACTURING CO LTD</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1.87%</t>
+          <t>2.25%</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.74%</t>
+          <t>1.02%</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>-1.13%</t>
+          <t>-1.23%</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>418400</v>
+        <v>3113000</v>
       </c>
       <c r="K35" t="n">
-        <v>174300</v>
+        <v>1717000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-244,100</t>
+          <t>-1,396,000</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-10-13_00990A_full_holdings.xlsx</t>
+          <t>2026-10-13_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>3533</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
+          <t>2308</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>台達電</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>嘉澤</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr"/>
+          <t>台達電</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>1.58%</t>
+        </is>
+      </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0.47%</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+          <t>2.01%</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>+0.43%</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>168000</v>
+      </c>
       <c r="K36" t="n">
-        <v>54000</v>
-      </c>
-      <c r="L36" t="inlineStr"/>
+        <v>270000</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>102,000</t>
+        </is>
+      </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-10-13_00407A_full_holdings.xlsx</t>
+          <t>2026-10-13_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>中華電</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
+          <t>國巨*</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>國巨*</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.04%</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
+          <t>2.21%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>1.74%</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>-0.47%</t>
+        </is>
+      </c>
       <c r="J37" t="n">
-        <v>64000</v>
-      </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
+        <v>699000</v>
+      </c>
+      <c r="K37" t="n">
+        <v>693000</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>-6,000</t>
+        </is>
+      </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-10-13_00407A_full_holdings.xlsx</t>
+          <t>2026-10-13_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2652,60 +2742,60 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2.29%</t>
+          <t>14.02%</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>1.79%</t>
+          <t>14.81%</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>-0.50%</t>
+          <t>+0.79%</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>50000</v>
+        <v>1112000</v>
       </c>
       <c r="K38" t="n">
-        <v>40000</v>
+        <v>1416000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-10,000</t>
+          <t>304,000</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-10-13_00407A_full_holdings.xlsx</t>
+          <t>2026-10-13_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2720,55 +2810,55 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>1.33%</t>
+          <t>1.02%</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>+0.73%</t>
+          <t>+1.02%</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>113000</v>
+        <v>1000</v>
       </c>
       <c r="K39" t="n">
-        <v>236000</v>
+        <v>1498000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>123,000</t>
+          <t>1,497,000</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-10-13_00407A_full_holdings.xlsx</t>
+          <t>2026-10-13_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2783,55 +2873,55 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0.71%</t>
+          <t>3.18%</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>1.03%</t>
+          <t>3.24%</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>+0.32%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>1350000</v>
+        <v>301000</v>
       </c>
       <c r="K40" t="n">
-        <v>1850000</v>
+        <v>378000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>500,000</t>
+          <t>77,000</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-10-13_00407A_full_holdings.xlsx</t>
+          <t>2026-10-13_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2841,60 +2931,60 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>5.02%</t>
+          <t>1.26%</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>4.72%</t>
+          <t>1.53%</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>-0.30%</t>
+          <t>+0.27%</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>143000</v>
+        <v>206000</v>
       </c>
       <c r="K41" t="n">
-        <v>128000</v>
+        <v>311000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-15,000</t>
+          <t>105,000</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-10-13_00407A_full_holdings.xlsx</t>
+          <t>2026-10-13_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2904,285 +2994,375 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2.41%</t>
+          <t>2.08%</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>2.14%</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>-1.06%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>324000</v>
+        <v>1175000</v>
       </c>
       <c r="K42" t="n">
-        <v>179000</v>
+        <v>1435000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-145,000</t>
+          <t>260,000</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-10-13_00407A_full_holdings.xlsx</t>
+          <t>2026-10-13_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2368</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr"/>
+          <t>2377</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>微星</t>
+        </is>
+      </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>金像電</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr"/>
+          <t>微星</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0.30%</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+          <t>1.04%</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>+1.04%</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>1000</v>
+      </c>
       <c r="K43" t="n">
-        <v>26000</v>
-      </c>
-      <c r="L43" t="inlineStr"/>
+        <v>1576000</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>1,575,000</t>
+        </is>
+      </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+          <t>2026-10-13_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2481</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr"/>
+          <t>2383</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>強茂</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr"/>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2.90%</t>
+        </is>
+      </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0.26%</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+          <t>3.54%</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>+0.64%</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>95000</v>
+      </c>
       <c r="K44" t="n">
-        <v>159000</v>
-      </c>
-      <c r="L44" t="inlineStr"/>
+        <v>152000</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>57,000</t>
+        </is>
+      </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+          <t>2026-10-13_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>5347</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr"/>
+          <t>2408</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>南亞科</t>
+        </is>
+      </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>世界</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr"/>
+          <t>南亞科</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1.14%</t>
+        </is>
+      </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>0.31%</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
+          <t>1.41%</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>+0.27%</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>434000</v>
+      </c>
       <c r="K45" t="n">
-        <v>177000</v>
-      </c>
-      <c r="L45" t="inlineStr"/>
+        <v>690000</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>256,000</t>
+        </is>
+      </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+          <t>2026-10-13_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>6271</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr"/>
+          <t>2412</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>中華電</t>
+        </is>
+      </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>同欣電</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr"/>
+          <t>中華電</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>1.37%</t>
+        </is>
+      </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>0.27%</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
+          <t>1.77%</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>+0.40%</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>1888000</v>
+      </c>
       <c r="K46" t="n">
-        <v>114000</v>
-      </c>
-      <c r="L46" t="inlineStr"/>
+        <v>2855000</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>967,000</t>
+        </is>
+      </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+          <t>2026-10-13_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>8996</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr"/>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>高力</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr"/>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>1.15%</t>
+        </is>
+      </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>1.71%</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+          <t>1.52%</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>+0.37%</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>50000</v>
+      </c>
       <c r="K47" t="n">
-        <v>100000</v>
-      </c>
-      <c r="L47" t="inlineStr"/>
+        <v>80000</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>30,000</t>
+        </is>
+      </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+          <t>2026-10-13_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3197,55 +3377,55 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>1.67%</t>
+          <t>1.25%</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>1.68%</t>
+          <t>1.54%</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.29%</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>174000</v>
+        <v>985000</v>
       </c>
       <c r="K48" t="n">
-        <v>178000</v>
+        <v>1391000</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>4,000</t>
+          <t>406,000</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+          <t>2026-10-13_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3255,60 +3435,60 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>1.12%</t>
+          <t>1.35%</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>1.54%</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="J49" t="n">
-        <v>11000</v>
+        <v>4270000</v>
       </c>
       <c r="K49" t="n">
-        <v>10000</v>
+        <v>5672000</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>-1,000</t>
+          <t>1,402,000</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+          <t>2026-10-13_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3323,55 +3503,55 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>1.16%</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>1.41%</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="J50" t="n">
-        <v>222000</v>
+        <v>11436000</v>
       </c>
       <c r="K50" t="n">
-        <v>227000</v>
+        <v>16386000</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>4,950,000</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+          <t>2026-10-13_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3386,55 +3566,55 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.71%</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>1.41%</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>185000</v>
+        <v>897000</v>
       </c>
       <c r="K51" t="n">
-        <v>189000</v>
+        <v>2104000</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>4,000</t>
+          <t>1,207,000</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+          <t>2026-10-13_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3449,55 +3629,55 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>8.35%</t>
+          <t>1.13%</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>8.26%</t>
+          <t>0.49%</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>-0.64%</t>
         </is>
       </c>
       <c r="J52" t="n">
-        <v>341000</v>
+        <v>31000</v>
       </c>
       <c r="K52" t="n">
-        <v>333000</v>
+        <v>16000</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>-8,000</t>
+          <t>-15,000</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+          <t>2026-10-13_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3512,55 +3692,55 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>2.12%</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>0.55%</t>
+          <t>2.00%</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="J53" t="n">
-        <v>23000</v>
+        <v>126000</v>
       </c>
       <c r="K53" t="n">
-        <v>25000</v>
+        <v>145000</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>19,000</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+          <t>2026-10-13_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3575,55 +3755,55 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>6.27%</t>
+          <t>3.59%</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>6.23%</t>
+          <t>3.24%</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.35%</t>
         </is>
       </c>
       <c r="J54" t="n">
-        <v>106000</v>
+        <v>3341000</v>
       </c>
       <c r="K54" t="n">
-        <v>113000</v>
+        <v>3650000</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>7,000</t>
+          <t>309,000</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+          <t>2026-10-13_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3633,60 +3813,60 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>漢唐</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>漢唐</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>2.09%</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>1.52%</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-0.57%</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>40000</v>
+        <v>335000</v>
       </c>
       <c r="K55" t="n">
-        <v>42000</v>
+        <v>307000</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>-28,000</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+          <t>2026-10-13_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3696,60 +3876,60 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>1.88%</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>1.83%</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>34000</v>
+        <v>125000</v>
       </c>
       <c r="K56" t="n">
-        <v>33000</v>
+        <v>160000</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>-1,000</t>
+          <t>35,000</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+          <t>2026-10-13_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3764,55 +3944,55 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>0.55%</t>
+          <t>1.31%</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>1.56%</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>96000</v>
+        <v>456000</v>
       </c>
       <c r="K57" t="n">
-        <v>98000</v>
+        <v>666000</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>210,000</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+          <t>2026-10-13_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3827,55 +4007,55 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>3491</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>昇達科</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>昇達科</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>6.26%</t>
+          <t>1.95%</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>6.17%</t>
+          <t>1.90%</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>518000</v>
+        <v>257000</v>
       </c>
       <c r="K58" t="n">
-        <v>526000</v>
+        <v>312000</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>8,000</t>
+          <t>55,000</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+          <t>2026-10-13_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3890,55 +4070,55 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>3042</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>晶技</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>晶技</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>3.52%</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>3.49%</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="J59" t="n">
-        <v>296000</v>
+        <v>99000</v>
       </c>
       <c r="K59" t="n">
-        <v>310000</v>
+        <v>119000</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>14,000</t>
+          <t>20,000</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+          <t>2026-10-13_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3953,55 +4133,55 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>2.63%</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>3.12%</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="J60" t="n">
-        <v>134000</v>
+        <v>5022000</v>
       </c>
       <c r="K60" t="n">
-        <v>136000</v>
+        <v>6914000</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>1,892,000</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+          <t>2026-10-13_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4011,60 +4191,60 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>1.34%</t>
+          <t>1.06%</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>1.33%</t>
+          <t>0.01%</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-1.05%</t>
         </is>
       </c>
       <c r="J61" t="n">
-        <v>46000</v>
+        <v>128000</v>
       </c>
       <c r="K61" t="n">
-        <v>49000</v>
+        <v>1000</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>-127,000</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+          <t>2026-10-13_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4079,55 +4259,55 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>0.92%</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.32%</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.40%</t>
         </is>
       </c>
       <c r="J62" t="n">
-        <v>204000</v>
+        <v>167000</v>
       </c>
       <c r="K62" t="n">
-        <v>214000</v>
+        <v>310000</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>143,000</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+          <t>2026-10-13_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4142,55 +4322,55 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>0.56%</t>
+          <t>1.58%</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>1.51%</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="J63" t="n">
-        <v>214000</v>
+        <v>336000</v>
       </c>
       <c r="K63" t="n">
-        <v>219000</v>
+        <v>389000</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>53,000</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+          <t>2026-10-13_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4205,55 +4385,55 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>昇達科</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>昇達科</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>4.28%</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>3.54%</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.74%</t>
         </is>
       </c>
       <c r="J64" t="n">
-        <v>62000</v>
+        <v>133000</v>
       </c>
       <c r="K64" t="n">
-        <v>64000</v>
+        <v>139000</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>6,000</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+          <t>2026-10-13_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4268,55 +4448,55 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>1815</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>富喬</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>富喬</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>1.82%</t>
+          <t>3.29%</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>1.85%</t>
+          <t>3.52%</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.23%</t>
         </is>
       </c>
       <c r="J65" t="n">
-        <v>248000</v>
+        <v>11420868</v>
       </c>
       <c r="K65" t="n">
-        <v>252000</v>
+        <v>12620868</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>4,000</t>
+          <t>1,200,000</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+          <t>2026-10-13_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4331,55 +4511,55 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2.30%</t>
+          <t>4.03%</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2.34%</t>
+          <t>3.94%</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="J66" t="n">
-        <v>411000</v>
+        <v>176000</v>
       </c>
       <c r="K66" t="n">
-        <v>427000</v>
+        <v>183000</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>16,000</t>
+          <t>7,000</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+          <t>2026-10-13_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4394,55 +4574,55 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>1.95%</t>
+          <t>0.42%</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>1.99%</t>
+          <t>0.41%</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="J67" t="n">
-        <v>121000</v>
+        <v>675000</v>
       </c>
       <c r="K67" t="n">
-        <v>125000</v>
+        <v>693000</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>4,000</t>
+          <t>18,000</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+          <t>2026-10-13_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4457,55 +4637,55 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>6.14%</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>6.22%</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="J68" t="n">
-        <v>387000</v>
+        <v>1116000</v>
       </c>
       <c r="K68" t="n">
-        <v>396000</v>
+        <v>1166000</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>9,000</t>
+          <t>50,000</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+          <t>2026-10-13_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4520,55 +4700,55 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>4.07%</t>
+          <t>5.66%</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>4.10%</t>
+          <t>5.49%</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="J69" t="n">
-        <v>244000</v>
+        <v>1227000</v>
       </c>
       <c r="K69" t="n">
-        <v>249000</v>
+        <v>1255000</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>28,000</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+          <t>2026-10-13_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4578,150 +4758,186 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>4.27%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2.17%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>-2.10%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J70" t="n">
-        <v>195191</v>
+        <v>201000</v>
       </c>
       <c r="K70" t="n">
-        <v>99191</v>
+        <v>206000</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>-96,000</t>
+          <t>5,000</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+          <t>2026-10-13_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>6147</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr"/>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>頎邦</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr"/>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2.17%</t>
+        </is>
+      </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>0.97%</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
+          <t>2.01%</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>-0.16%</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>424000</v>
+      </c>
       <c r="K71" t="n">
-        <v>1293000</v>
-      </c>
-      <c r="L71" t="inlineStr"/>
+        <v>426000</v>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>2026-10-13_00400A_full_holdings.xlsx</t>
+          <t>2026-10-13_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>元大金</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr"/>
+          <t>技嘉</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>技嘉</t>
+        </is>
+      </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>0.05%</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
+          <t>0.40%</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>0.41%</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
       <c r="J72" t="n">
-        <v>241040</v>
-      </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
+        <v>520000</v>
+      </c>
+      <c r="K72" t="n">
+        <v>534000</v>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>14,000</t>
+        </is>
+      </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>2026-10-13_00400A_full_holdings.xlsx</t>
+          <t>2026-10-13_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4736,55 +4952,55 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>漢唐</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>漢唐</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>0.42%</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>1.93%</t>
+          <t>0.41%</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>+0.95%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="J73" t="n">
-        <v>2096000</v>
+        <v>158000</v>
       </c>
       <c r="K73" t="n">
-        <v>4192000</v>
+        <v>166000</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2,096,000</t>
+          <t>8,000</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2026-10-13_00400A_full_holdings.xlsx</t>
+          <t>2026-10-13_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4794,60 +5010,60 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>4.10%</t>
+          <t>4.65%</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2.75%</t>
+          <t>5.04%</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>-1.35%</t>
+          <t>+0.39%</t>
         </is>
       </c>
       <c r="J74" t="n">
-        <v>669000</v>
+        <v>293000</v>
       </c>
       <c r="K74" t="n">
-        <v>475000</v>
+        <v>323000</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>-194,000</t>
+          <t>30,000</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>2026-10-13_00400A_full_holdings.xlsx</t>
+          <t>2026-10-13_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4862,55 +5078,55 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>6.55%</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>1.44%</t>
+          <t>6.47%</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>+0.48%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="J75" t="n">
-        <v>469000</v>
+        <v>894000</v>
       </c>
       <c r="K75" t="n">
-        <v>708000</v>
+        <v>921000</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>239,000</t>
+          <t>27,000</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>2026-10-13_00400A_full_holdings.xlsx</t>
+          <t>2026-10-13_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4925,55 +5141,55 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>禾伸堂</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>禾伸堂</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>8.47%</t>
+          <t>0.49%</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>8.85%</t>
+          <t>0.63%</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>+0.38%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="J76" t="n">
-        <v>1034000</v>
+        <v>267000</v>
       </c>
       <c r="K76" t="n">
-        <v>1094000</v>
+        <v>367000</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>60,000</t>
+          <t>100,000</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>2026-10-13_00400A_full_holdings.xlsx</t>
+          <t>2026-10-13_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4988,55 +5204,55 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>0.42%</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>0.40%</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>+1.49%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="J77" t="n">
-        <v>378000</v>
+        <v>64000</v>
       </c>
       <c r="K77" t="n">
-        <v>734000</v>
+        <v>69000</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>356,000</t>
+          <t>5,000</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>2026-10-13_00400A_full_holdings.xlsx</t>
+          <t>2026-10-13_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5046,60 +5262,60 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>5.59%</t>
+          <t>1.97%</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>4.55%</t>
+          <t>2.03%</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>-1.04%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="J78" t="n">
-        <v>282000</v>
+        <v>860013</v>
       </c>
       <c r="K78" t="n">
-        <v>254000</v>
+        <v>910013</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>-28,000</t>
+          <t>50,000</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>2026-10-13_00400A_full_holdings.xlsx</t>
+          <t>2026-10-13_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5114,55 +5330,55 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>3.40%</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>1.60%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>+0.64%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="J79" t="n">
-        <v>1169000</v>
+        <v>194000</v>
       </c>
       <c r="K79" t="n">
-        <v>1871000</v>
+        <v>202000</v>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>702,000</t>
+          <t>8,000</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>2026-10-13_00400A_full_holdings.xlsx</t>
+          <t>2026-10-13_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5177,55 +5393,55 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2637</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>慧洋-KY</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>慧洋-KY</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>0.53%</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>1.03%</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>+0.21%</t>
+          <t>+0.50%</t>
         </is>
       </c>
       <c r="J80" t="n">
-        <v>834000</v>
+        <v>34000</v>
       </c>
       <c r="K80" t="n">
-        <v>1424000</v>
+        <v>69000</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>590,000</t>
+          <t>35,000</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>2026-10-13_00400A_full_holdings.xlsx</t>
+          <t>2026-10-13_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5240,55 +5456,55 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>0.69%</t>
+          <t>5.92%</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>6.01%</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>+0.83%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="J81" t="n">
-        <v>3054000</v>
+        <v>1161000</v>
       </c>
       <c r="K81" t="n">
-        <v>6547000</v>
+        <v>1241000</v>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>3,493,000</t>
+          <t>80,000</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>2026-10-13_00400A_full_holdings.xlsx</t>
+          <t>2026-10-13_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5303,55 +5519,55 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
+          <t>0.42%</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
           <t>1.20%</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>1.59%</t>
-        </is>
-      </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>+0.39%</t>
+          <t>+0.78%</t>
         </is>
       </c>
       <c r="J82" t="n">
-        <v>51000</v>
+        <v>255000</v>
       </c>
       <c r="K82" t="n">
-        <v>71000</v>
+        <v>755000</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>500,000</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>2026-10-13_00400A_full_holdings.xlsx</t>
+          <t>2026-10-13_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5361,60 +5577,60 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>4.12%</t>
+          <t>1.26%</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>3.54%</t>
+          <t>1.42%</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>-0.58%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="J83" t="n">
-        <v>377000</v>
+        <v>1000000</v>
       </c>
       <c r="K83" t="n">
-        <v>329000</v>
+        <v>1200000</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>-48,000</t>
+          <t>200,000</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>2026-10-13_00400A_full_holdings.xlsx</t>
+          <t>2026-10-13_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5424,60 +5640,60 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>5289</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>宜鼎</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>宜鼎</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>4.89%</t>
+          <t>0.41%</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>4.11%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>-0.78%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="J84" t="n">
-        <v>1209000</v>
+        <v>149952</v>
       </c>
       <c r="K84" t="n">
-        <v>1069000</v>
+        <v>152952</v>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>-140,000</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>2026-10-13_00400A_full_holdings.xlsx</t>
+          <t>2026-10-13_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5492,55 +5708,55 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>1.93%</t>
+          <t>0.42%</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2.52%</t>
+          <t>0.41%</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="J85" t="n">
-        <v>1034000</v>
+        <v>256000</v>
       </c>
       <c r="K85" t="n">
-        <v>1287000</v>
+        <v>266000</v>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>253,000</t>
+          <t>10,000</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>2026-10-13_00400A_full_holdings.xlsx</t>
+          <t>2026-10-13_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5555,55 +5771,55 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.49%</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>0.95%</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>+0.48%</t>
+          <t>+0.46%</t>
         </is>
       </c>
       <c r="J86" t="n">
-        <v>819000</v>
+        <v>134000</v>
       </c>
       <c r="K86" t="n">
-        <v>1614000</v>
+        <v>278000</v>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>795,000</t>
+          <t>144,000</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>2026-10-13_00400A_full_holdings.xlsx</t>
+          <t>2026-10-13_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5613,114 +5829,3867 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>4.06%</t>
+          <t>0.67%</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>3.54%</t>
+          <t>0.82%</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>-0.52%</t>
+          <t>+0.15%</t>
         </is>
       </c>
       <c r="J87" t="n">
-        <v>176000</v>
+        <v>379000</v>
       </c>
       <c r="K87" t="n">
-        <v>154000</v>
+        <v>479000</v>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>-22,000</t>
+          <t>100,000</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>2026-10-13_00400A_full_holdings.xlsx</t>
+          <t>2026-10-13_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>6223</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>4.57%</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>4.63%</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>+0.06%</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>344000</v>
+      </c>
+      <c r="K88" t="n">
+        <v>364000</v>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>2026-10-13_00992A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>6274</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>0.50%</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>0.65%</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>+0.15%</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
+        <v>133000</v>
+      </c>
+      <c r="K89" t="n">
+        <v>183000</v>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>50,000</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>2026-10-13_00992A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>0.68%</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>0.70%</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>+0.02%</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>52000</v>
+      </c>
+      <c r="K90" t="n">
+        <v>57000</v>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>2026-10-13_00992A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>8046</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>3.07%</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>3.11%</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>+0.04%</t>
+        </is>
+      </c>
+      <c r="J91" t="n">
+        <v>986000</v>
+      </c>
+      <c r="K91" t="n">
+        <v>1007000</v>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>21,000</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>2026-10-13_00992A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>8150</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>南茂</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>南茂</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>0.53%</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>0.51%</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
+        </is>
+      </c>
+      <c r="J92" t="n">
+        <v>1991000</v>
+      </c>
+      <c r="K92" t="n">
+        <v>2032000</v>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>41,000</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>2026-10-13_00992A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>8996</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>6.07%</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>6.11%</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>+0.04%</t>
+        </is>
+      </c>
+      <c r="J93" t="n">
+        <v>1630000</v>
+      </c>
+      <c r="K93" t="n">
+        <v>1663000</v>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>33,000</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>2026-10-13_00992A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>00990A</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2368</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>0.50%</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="n">
+        <v>156000</v>
+      </c>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>2026-10-13_00990A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>00990A</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>0.51%</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="n">
+        <v>23000</v>
+      </c>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>2026-10-13_00990A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>00990A</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>0091</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>50SAMSUNG ELECTRO-MECHANICS CO</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>0.71%</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="n">
+        <v>7234</v>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>2026-10-13_00990A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>00990A</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2308</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>台達電</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>台達電</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>3.33%</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>2.04%</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>-1.29%</t>
+        </is>
+      </c>
+      <c r="J97" t="n">
+        <v>633000</v>
+      </c>
+      <c r="K97" t="n">
+        <v>420000</v>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>-213,000</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>2026-10-13_00990A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>00990A</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>6981</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>MURATA MANUFACTURING CO LTD</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>MURATA MANUFACTURING CO LTD</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>1.87%</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>0.74%</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>-1.13%</t>
+        </is>
+      </c>
+      <c r="J98" t="n">
+        <v>418400</v>
+      </c>
+      <c r="K98" t="n">
+        <v>174300</v>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>-244,100</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>2026-10-13_00990A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>00407A</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>3533</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>嘉澤</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>0.47%</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="n">
+        <v>54000</v>
+      </c>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>2026-10-13_00407A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>00407A</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>2412</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>中華電</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>0.04%</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="n">
+        <v>64000</v>
+      </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>2026-10-13_00407A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>00407A</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2059</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>川湖</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>川湖</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>2.29%</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>1.79%</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>-0.50%</t>
+        </is>
+      </c>
+      <c r="J101" t="n">
+        <v>50000</v>
+      </c>
+      <c r="K101" t="n">
+        <v>40000</v>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>-10,000</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>2026-10-13_00407A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>00407A</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>2368</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>0.60%</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>1.33%</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>+0.73%</t>
+        </is>
+      </c>
+      <c r="J102" t="n">
+        <v>113000</v>
+      </c>
+      <c r="K102" t="n">
+        <v>236000</v>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>123,000</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>2026-10-13_00407A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>00407A</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>2615</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>萬海</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>萬海</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>0.71%</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>1.03%</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>+0.32%</t>
+        </is>
+      </c>
+      <c r="J103" t="n">
+        <v>1350000</v>
+      </c>
+      <c r="K103" t="n">
+        <v>1850000</v>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>500,000</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>2026-10-13_00407A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>00407A</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>5.02%</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>4.72%</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>-0.30%</t>
+        </is>
+      </c>
+      <c r="J104" t="n">
+        <v>143000</v>
+      </c>
+      <c r="K104" t="n">
+        <v>128000</v>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>-15,000</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>2026-10-13_00407A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>00407A</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>8996</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>2.41%</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>1.35%</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>-1.06%</t>
+        </is>
+      </c>
+      <c r="J105" t="n">
+        <v>324000</v>
+      </c>
+      <c r="K105" t="n">
+        <v>179000</v>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>-145,000</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>2026-10-13_00407A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>2368</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>0.30%</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="n">
+        <v>26000</v>
+      </c>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>2481</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>強茂</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>0.26%</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="n">
+        <v>159000</v>
+      </c>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>5347</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>世界</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>0.31%</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="n">
+        <v>177000</v>
+      </c>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>6271</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>同欣電</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>0.27%</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="n">
+        <v>114000</v>
+      </c>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>8996</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>1.71%</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="n">
+        <v>100000</v>
+      </c>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>1560</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>中砂</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>中砂</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>1.67%</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>1.68%</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="J111" t="n">
+        <v>174000</v>
+      </c>
+      <c r="K111" t="n">
+        <v>178000</v>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>2059</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>川湖</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>川湖</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>1.12%</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>1.00%</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>-0.12%</t>
+        </is>
+      </c>
+      <c r="J112" t="n">
+        <v>11000</v>
+      </c>
+      <c r="K112" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>光寶科</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>光寶科</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>0.62%</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>0.62%</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="J113" t="n">
+        <v>222000</v>
+      </c>
+      <c r="K113" t="n">
+        <v>227000</v>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>2313</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>華通</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>華通</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>0.45%</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>0.46%</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="J114" t="n">
+        <v>185000</v>
+      </c>
+      <c r="K114" t="n">
+        <v>189000</v>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>8.35%</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>8.26%</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>-0.09%</t>
+        </is>
+      </c>
+      <c r="J115" t="n">
+        <v>341000</v>
+      </c>
+      <c r="K115" t="n">
+        <v>333000</v>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>-8,000</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>0.52%</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>0.55%</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>+0.03%</t>
+        </is>
+      </c>
+      <c r="J116" t="n">
+        <v>23000</v>
+      </c>
+      <c r="K116" t="n">
+        <v>25000</v>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>2383</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>6.27%</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>6.23%</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>-0.04%</t>
+        </is>
+      </c>
+      <c r="J117" t="n">
+        <v>106000</v>
+      </c>
+      <c r="K117" t="n">
+        <v>113000</v>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>2404</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>漢唐</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>漢唐</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>0.48%</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>0.48%</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="J118" t="n">
+        <v>40000</v>
+      </c>
+      <c r="K118" t="n">
+        <v>42000</v>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>1.51%</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>1.48%</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>-0.03%</t>
+        </is>
+      </c>
+      <c r="J119" t="n">
+        <v>34000</v>
+      </c>
+      <c r="K119" t="n">
+        <v>33000</v>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>2467</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>志聖</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>志聖</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>0.55%</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>0.54%</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="J120" t="n">
+        <v>96000</v>
+      </c>
+      <c r="K120" t="n">
+        <v>98000</v>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>6.26%</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>6.17%</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>-0.09%</t>
+        </is>
+      </c>
+      <c r="J121" t="n">
+        <v>518000</v>
+      </c>
+      <c r="K121" t="n">
+        <v>526000</v>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>3042</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>晶技</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>晶技</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>0.58%</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>0.60%</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>+0.02%</t>
+        </is>
+      </c>
+      <c r="J122" t="n">
+        <v>296000</v>
+      </c>
+      <c r="K122" t="n">
+        <v>310000</v>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>14,000</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>3044</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>健鼎</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>健鼎</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>0.75%</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>0.77%</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>+0.02%</t>
+        </is>
+      </c>
+      <c r="J123" t="n">
+        <v>134000</v>
+      </c>
+      <c r="K123" t="n">
+        <v>136000</v>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>3081</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>聯亞</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>聯亞</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>1.34%</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>1.33%</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="J124" t="n">
+        <v>46000</v>
+      </c>
+      <c r="K124" t="n">
+        <v>49000</v>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>3105</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>穩懋</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>穩懋</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>1.14%</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>1.18%</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>+0.04%</t>
+        </is>
+      </c>
+      <c r="J125" t="n">
+        <v>204000</v>
+      </c>
+      <c r="K125" t="n">
+        <v>214000</v>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>3264</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>欣銓</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>欣銓</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>0.56%</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>0.58%</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>+0.02%</t>
+        </is>
+      </c>
+      <c r="J126" t="n">
+        <v>214000</v>
+      </c>
+      <c r="K126" t="n">
+        <v>219000</v>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>3491</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>昇達科</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>昇達科</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>0.91%</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>0.92%</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="J127" t="n">
+        <v>62000</v>
+      </c>
+      <c r="K127" t="n">
+        <v>64000</v>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>3711</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>1.82%</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>1.85%</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>+0.03%</t>
+        </is>
+      </c>
+      <c r="J128" t="n">
+        <v>248000</v>
+      </c>
+      <c r="K128" t="n">
+        <v>252000</v>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>4958</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>2.30%</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>2.34%</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>+0.04%</t>
+        </is>
+      </c>
+      <c r="J129" t="n">
+        <v>411000</v>
+      </c>
+      <c r="K129" t="n">
+        <v>427000</v>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>16,000</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>6187</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>萬潤</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>萬潤</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>1.95%</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>1.99%</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>+0.04%</t>
+        </is>
+      </c>
+      <c r="J130" t="n">
+        <v>121000</v>
+      </c>
+      <c r="K130" t="n">
+        <v>125000</v>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>6257</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>矽格</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>矽格</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>1.07%</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>1.10%</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>+0.03%</t>
+        </is>
+      </c>
+      <c r="J131" t="n">
+        <v>387000</v>
+      </c>
+      <c r="K131" t="n">
+        <v>396000</v>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>6274</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>4.07%</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>4.10%</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>+0.03%</t>
+        </is>
+      </c>
+      <c r="J132" t="n">
+        <v>244000</v>
+      </c>
+      <c r="K132" t="n">
+        <v>249000</v>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>4.27%</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>2.17%</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>-2.10%</t>
+        </is>
+      </c>
+      <c r="J133" t="n">
+        <v>195191</v>
+      </c>
+      <c r="K133" t="n">
+        <v>99191</v>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>-96,000</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>2026-10-13_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
           <t>00400A</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>6147</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>頎邦</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr"/>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>0.97%</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="n">
+        <v>1293000</v>
+      </c>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>2026-10-13_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>2885</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>元大金</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>0.05%</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="n">
+        <v>241040</v>
+      </c>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>2026-10-13_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>2303</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>0.98%</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>1.93%</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>+0.95%</t>
+        </is>
+      </c>
+      <c r="J136" t="n">
+        <v>2096000</v>
+      </c>
+      <c r="K136" t="n">
+        <v>4192000</v>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>2,096,000</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>2026-10-13_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>2308</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>台達電</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>台達電</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>4.10%</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>2.75%</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>-1.35%</t>
+        </is>
+      </c>
+      <c r="J137" t="n">
+        <v>669000</v>
+      </c>
+      <c r="K137" t="n">
+        <v>475000</v>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>-194,000</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>2026-10-13_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>2327</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>國巨*</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>國巨*</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>0.96%</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>1.44%</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>+0.48%</t>
+        </is>
+      </c>
+      <c r="J138" t="n">
+        <v>469000</v>
+      </c>
+      <c r="K138" t="n">
+        <v>708000</v>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>239,000</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>2026-10-13_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>8.47%</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>8.85%</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>+0.38%</t>
+        </is>
+      </c>
+      <c r="J139" t="n">
+        <v>1034000</v>
+      </c>
+      <c r="K139" t="n">
+        <v>1094000</v>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>60,000</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>2026-10-13_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>2368</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>1.51%</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>3.00%</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>+1.49%</t>
+        </is>
+      </c>
+      <c r="J140" t="n">
+        <v>378000</v>
+      </c>
+      <c r="K140" t="n">
+        <v>734000</v>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>356,000</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>2026-10-13_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>2383</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>5.59%</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>4.55%</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>-1.04%</t>
+        </is>
+      </c>
+      <c r="J141" t="n">
+        <v>282000</v>
+      </c>
+      <c r="K141" t="n">
+        <v>254000</v>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>-28,000</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>2026-10-13_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>2603</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>長榮</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>長榮</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>0.96%</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>1.60%</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>+0.64%</t>
+        </is>
+      </c>
+      <c r="J142" t="n">
+        <v>1169000</v>
+      </c>
+      <c r="K142" t="n">
+        <v>1871000</v>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>702,000</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>2026-10-13_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>2637</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>慧洋-KY</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>慧洋-KY</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>0.27%</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>0.48%</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>+0.21%</t>
+        </is>
+      </c>
+      <c r="J143" t="n">
+        <v>834000</v>
+      </c>
+      <c r="K143" t="n">
+        <v>1424000</v>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>590,000</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>2026-10-13_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>2891</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>中信金</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>中信金</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>0.69%</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>1.52%</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>+0.83%</t>
+        </is>
+      </c>
+      <c r="J144" t="n">
+        <v>3054000</v>
+      </c>
+      <c r="K144" t="n">
+        <v>6547000</v>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>3,493,000</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>2026-10-13_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>3008</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>1.20%</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>1.59%</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>+0.39%</t>
+        </is>
+      </c>
+      <c r="J145" t="n">
+        <v>51000</v>
+      </c>
+      <c r="K145" t="n">
+        <v>71000</v>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>2026-10-13_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>4.12%</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>3.54%</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>-0.58%</t>
+        </is>
+      </c>
+      <c r="J146" t="n">
+        <v>377000</v>
+      </c>
+      <c r="K146" t="n">
+        <v>329000</v>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>-48,000</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>2026-10-13_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>4.89%</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>4.11%</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>-0.78%</t>
+        </is>
+      </c>
+      <c r="J147" t="n">
+        <v>1209000</v>
+      </c>
+      <c r="K147" t="n">
+        <v>1069000</v>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>-140,000</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>2026-10-13_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>3044</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>健鼎</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>健鼎</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>1.93%</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>2.52%</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>+0.59%</t>
+        </is>
+      </c>
+      <c r="J148" t="n">
+        <v>1034000</v>
+      </c>
+      <c r="K148" t="n">
+        <v>1287000</v>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>253,000</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>2026-10-13_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>3231</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>0.50%</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>0.98%</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>+0.48%</t>
+        </is>
+      </c>
+      <c r="J149" t="n">
+        <v>819000</v>
+      </c>
+      <c r="K149" t="n">
+        <v>1614000</v>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>795,000</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>2026-10-13_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>3653</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>4.06%</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>3.54%</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>-0.52%</t>
+        </is>
+      </c>
+      <c r="J150" t="n">
+        <v>176000</v>
+      </c>
+      <c r="K150" t="n">
+        <v>154000</v>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>-22,000</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>2026-10-13_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
         <is>
           <t>6187</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="E151" t="inlineStr">
         <is>
           <t>萬潤</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
+      <c r="F151" t="inlineStr">
         <is>
           <t>萬潤</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="G151" t="inlineStr">
         <is>
           <t>3.22%</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
+      <c r="H151" t="inlineStr">
         <is>
           <t>1.48%</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
+      <c r="I151" t="inlineStr">
         <is>
           <t>-1.74%</t>
         </is>
       </c>
-      <c r="J88" t="n">
+      <c r="J151" t="n">
         <v>596000</v>
       </c>
-      <c r="K88" t="n">
+      <c r="K151" t="n">
         <v>295000</v>
       </c>
-      <c r="L88" t="inlineStr">
+      <c r="L151" t="inlineStr">
         <is>
           <t>-301,000</t>
         </is>
       </c>
-      <c r="M88" t="inlineStr">
+      <c r="M151" t="inlineStr">
         <is>
           <t>2026-10-13_00400A_full_holdings.xlsx</t>
         </is>
